--- a/sampleprojects/TaxReturn/excel/states/DC.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/DC.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $30,000 std ded, 10.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 30000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $22,500 std ded, 10.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 22500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
   </si>
   <si>
     <t>Default (Single/MFS): $15,000 std ded, 10.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 15000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.1075</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/DC.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/DC.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>DT: DC Tax</t>
   </si>
@@ -293,7 +293,7 @@
     <t>62.0</t>
   </si>
   <si>
-    <t>DC minimum age for military retirement exemption (62)</t>
+    <t>Age 62 test of the former DC military retired pay exclusion (D.C. Code 47-1803.02(a)(2)(N)(i)), which applies only to taxable years before 2015; kept for the survivor-benefit subtraction on D-40 line 12, which still requires age 62 (#1330).</t>
   </si>
   <si>
     <t>dc_military_retirement_exemption</t>
@@ -302,16 +302,13 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>DC military retirement exemption (computed based on age)</t>
+    <t>DC military retirement exemption (computed): 0 for 2025, the exclusion having been repealed for taxable years from 2015 (D.C. Law 20-155). See dc_military_retirement_exemption_amount (#1330).</t>
   </si>
   <si>
     <t>dc_military_retirement_exemption_amount</t>
   </si>
   <si>
-    <t>3000.0</t>
-  </si>
-  <si>
-    <t>DC military retirement exemption - $3,000 only if age 62+ (2025). Source: MOAA</t>
+    <t>DC has no exclusion for military retired pay in 2025: the $3,000 exclusion for taxpayers 62 or older in D.C. Code 47-1803.02(a)(2)(N)(i) applies only to taxable years beginning before January 1, 2015 (repealed by the Fiscal Year 2015 Budget Support Act, D.C. Law 20-155), and the 2025 D-40 booklet and Schedule I carry no military subtraction. Only survivor benefits (D-40 line 12, age 62+) remain (#1330).</t>
   </si>
   <si>
     <t>dc_military_retirement_taxable</t>
@@ -2346,7 +2343,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
@@ -2355,7 +2352,7 @@
         <v>52</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -2378,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>50</v>
@@ -2396,7 +2393,7 @@
         <v>52</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -2419,7 +2416,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>50</v>
@@ -2428,7 +2425,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
@@ -2437,7 +2434,7 @@
         <v>52</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -2460,7 +2457,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>50</v>
@@ -2469,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
@@ -2478,7 +2475,7 @@
         <v>52</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -2501,7 +2498,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>50</v>
@@ -2510,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
@@ -2519,7 +2516,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -2542,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>50</v>
@@ -2560,7 +2557,7 @@
         <v>52</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
